--- a/downloads/exportExcelInternalJObFilter1.xlsx
+++ b/downloads/exportExcelInternalJObFilter1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
   <si>
     <t>Job ID</t>
   </si>
@@ -85,31 +85,16 @@
     <t>In progressDX</t>
   </si>
   <si>
-    <t>J-691</t>
+    <t>J-707</t>
   </si>
   <si>
     <t>9863574112</t>
   </si>
   <si>
-    <t>28/02/2026</t>
-  </si>
-  <si>
-    <t>J-686</t>
-  </si>
-  <si>
-    <t>25/02/2026</t>
-  </si>
-  <si>
-    <t>J-683</t>
-  </si>
-  <si>
-    <t>J-665</t>
-  </si>
-  <si>
     <t>doneJob</t>
   </si>
   <si>
-    <t>21/02/2026</t>
+    <t>02/03/2026</t>
   </si>
 </sst>
 </file>
@@ -486,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -614,136 +599,13 @@
         <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
